--- a/converted/tozalangan/baliqchi/Avgust/Elektr Murojaatlar.xlsx
+++ b/converted/tozalangan/baliqchi/Avgust/Elektr Murojaatlar.xlsx
@@ -11,11 +11,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
   <si>
     <t>Murojaatlar Avgust Holatiga Ko'ra</t>
   </si>
   <si>
+    <t>Podstansiya</t>
+  </si>
+  <si>
+    <t>Fider</t>
+  </si>
+  <si>
     <t>TP Nomi</t>
   </si>
   <si>
@@ -46,9 +52,18 @@
     <t>Holati (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
+    <t>Baliqchi</t>
+  </si>
+  <si>
+    <t>Oqqo'rg'on</t>
+  </si>
+  <si>
     <t>665</t>
   </si>
   <si>
@@ -82,6 +97,9 @@
     <t>Sahovat MFY</t>
   </si>
   <si>
+    <t>TP 515 shu hududning Transformatorlar fayllarida ham, abonentlar reestrida ham yo'q - TP ga bog'lanmaydi</t>
+  </si>
+  <si>
     <t>baliqchi/Avgust/Elektr Murojaatlar.xlsx, 4-qator</t>
   </si>
   <si>
@@ -100,9 +118,15 @@
     <t>Yangi</t>
   </si>
   <si>
+    <t>TP o'rnida "Yangi" yozilgan - TP bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>baliqchi/Avgust/Elektr Murojaatlar.xlsx, 5-qator</t>
   </si>
   <si>
+    <t>Sarkor</t>
+  </si>
+  <si>
     <t>246</t>
   </si>
   <si>
@@ -160,6 +184,9 @@
     <t>Alchazor MFY</t>
   </si>
   <si>
+    <t>TP 222 shu hududning Transformatorlar fayllarida yo'q - TP bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>baliqchi/Avgust/Elektr Murojaatlar.xlsx, 9-qator</t>
   </si>
   <si>
@@ -173,6 +200,9 @@
   </si>
   <si>
     <t>Afsona MFY</t>
+  </si>
+  <si>
+    <t>TP 405 shu hududning Transformatorlar fayllarida ham, abonentlar reestrida ham yo'q - TP ga bog'lanmaydi</t>
   </si>
   <si>
     <t>baliqchi/Avgust/Elektr Murojaatlar.xlsx, 10-qator</t>
@@ -593,17 +623,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="7" width="22" customWidth="1"/>
-    <col min="8" max="11" width="26" customWidth="1"/>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="9" width="22" customWidth="1"/>
+    <col min="10" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -617,8 +647,11 @@
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -640,10 +673,10 @@
       <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="4" t="s">
@@ -652,245 +685,287 @@
       <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1">
         <v>46247</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46251</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46252</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46254</v>
+      </c>
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="8" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46259</v>
+      </c>
+      <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="H8" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1">
-        <v>46251</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="I8" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
         <v>23</v>
       </c>
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46252</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" t="s">
-        <v>29</v>
+    <row r="9" spans="4:14" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46260</v>
+      </c>
+      <c r="G9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46252</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46254</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46259</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46260</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="1">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="1">
         <v>46247</v>
       </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
       <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" t="s">
-        <v>54</v>
+        <v>62</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
